--- a/examples/sample-report/sample-calendar.xlsx
+++ b/examples/sample-report/sample-calendar.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,6 +48,10 @@
     <font>
       <b val="1"/>
       <color rgb="000B0B0B"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
+      <u val="single"/>
     </font>
     <font>
       <color rgb="000CA30C"/>
@@ -127,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -163,6 +167,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -180,19 +187,22 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -822,7 +832,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Ask something they actually want to answer, and make it about them rather than about you.</t>
+          <t>Ask something they actually want to answer. Make it about them, not you.</t>
         </is>
       </c>
     </row>
@@ -834,7 +844,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>The direct revenue driver. One per five days is the right frequency — more than that and it reads as desperate.</t>
+          <t>The direct sales post. One every five days is right — more, and it reads as desperate.</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -856,7 +866,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Describe their exact frustration in the words they use in their own head. Sell nothing at all. Just mirror it back.</t>
+          <t>Describe their frustration in their own words. Sell nothing. Just mirror it back.</t>
         </is>
       </c>
     </row>
@@ -985,12 +995,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -1008,7 +1018,7 @@
           <t>Teach one thing about understood and properly that most people get wrong.</t>
         </is>
       </c>
-      <c r="G5" s="13" t="inlineStr">
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>3 ways to fix your framing in under a minute</t>
         </is>
@@ -1018,64 +1028,64 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="I5" s="14" t="inlineStr">
+      <c r="I5" s="15" t="inlineStr">
         <is>
           <t>solid evidence</t>
         </is>
       </c>
-      <c r="J5" s="15" t="inlineStr"/>
-      <c r="K5" s="16" t="inlineStr"/>
-      <c r="L5" s="16" t="inlineStr"/>
-      <c r="M5" s="15" t="inlineStr"/>
+      <c r="J5" s="16" t="inlineStr"/>
+      <c r="K5" s="17" t="inlineStr"/>
+      <c r="L5" s="17" t="inlineStr"/>
+      <c r="M5" s="16" t="inlineStr"/>
     </row>
     <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="17" t="n">
+      <c r="A6" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>PROOF</t>
         </is>
       </c>
-      <c r="E6" s="19" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>Public / Building / Smallbusiness</t>
         </is>
       </c>
-      <c r="F6" s="19" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>Show a real result from public and building — where it started, what you changed, where it ended.</t>
         </is>
       </c>
-      <c r="G6" s="19" t="inlineStr">
+      <c r="G6" s="21" t="inlineStr">
         <is>
           <t>Day 30 of building this in public</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="18" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="I6" s="20" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t>early signal</t>
         </is>
       </c>
-      <c r="J6" s="15" t="inlineStr"/>
-      <c r="K6" s="16" t="inlineStr"/>
-      <c r="L6" s="16" t="inlineStr"/>
-      <c r="M6" s="15" t="inlineStr"/>
+      <c r="J6" s="16" t="inlineStr"/>
+      <c r="K6" s="17" t="inlineStr"/>
+      <c r="L6" s="17" t="inlineStr"/>
+      <c r="M6" s="16" t="inlineStr"/>
     </row>
     <row r="7" ht="40" customHeight="1">
       <c r="A7" s="11" t="n">
@@ -1083,15 +1093,15 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>ENGAGE</t>
         </is>
@@ -1106,7 +1116,7 @@
           <t>Ask your audience the one thing you most want to know about how they approach asked and gear.</t>
         </is>
       </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>You asked, so here it is: gear</t>
         </is>
@@ -1116,64 +1126,64 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="I7" s="22" t="inlineStr">
+      <c r="I7" s="24" t="inlineStr">
         <is>
           <t>not enough data yet</t>
         </is>
       </c>
-      <c r="J7" s="15" t="inlineStr"/>
-      <c r="K7" s="16" t="inlineStr"/>
-      <c r="L7" s="16" t="inlineStr"/>
-      <c r="M7" s="15" t="inlineStr"/>
+      <c r="J7" s="16" t="inlineStr"/>
+      <c r="K7" s="17" t="inlineStr"/>
+      <c r="L7" s="17" t="inlineStr"/>
+      <c r="M7" s="16" t="inlineStr"/>
     </row>
     <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="17" t="n">
+      <c r="A8" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>OFFER</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>Looked / Howto</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>Make one specific, time-bound offer connected to looked and howto. Say exactly what they get and exactly what to do.</t>
         </is>
       </c>
-      <c r="G8" s="19" t="inlineStr">
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>What 30 months of this actually looked like</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H8" s="18" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="I8" s="24" t="inlineStr">
+      <c r="I8" s="26" t="inlineStr">
         <is>
           <t>not enough data yet</t>
         </is>
       </c>
-      <c r="J8" s="15" t="inlineStr"/>
-      <c r="K8" s="16" t="inlineStr"/>
-      <c r="L8" s="16" t="inlineStr"/>
-      <c r="M8" s="15" t="inlineStr"/>
+      <c r="J8" s="16" t="inlineStr"/>
+      <c r="K8" s="17" t="inlineStr"/>
+      <c r="L8" s="17" t="inlineStr"/>
+      <c r="M8" s="16" t="inlineStr"/>
     </row>
     <row r="9" ht="40" customHeight="1">
       <c r="A9" s="11" t="n">
@@ -1181,15 +1191,15 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="D9" s="25" t="inlineStr">
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
         <is>
           <t>MIRROR</t>
         </is>
@@ -1204,7 +1214,7 @@
           <t>Describe the frustration someone hits with replying and pricing, in their words, and sell nothing.</t>
         </is>
       </c>
-      <c r="G9" s="13" t="inlineStr">
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t>Replying to a comment about software</t>
         </is>
@@ -1214,28 +1224,28 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="I9" s="24" t="inlineStr">
         <is>
           <t>not enough data yet</t>
         </is>
       </c>
-      <c r="J9" s="15" t="inlineStr"/>
-      <c r="K9" s="16" t="inlineStr"/>
-      <c r="L9" s="16" t="inlineStr"/>
-      <c r="M9" s="15" t="inlineStr"/>
+      <c r="J9" s="16" t="inlineStr"/>
+      <c r="K9" s="17" t="inlineStr"/>
+      <c r="L9" s="17" t="inlineStr"/>
+      <c r="M9" s="16" t="inlineStr"/>
     </row>
     <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="17" t="n">
+      <c r="A10" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -1243,35 +1253,35 @@
           <t>EDUCATE</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>Numbers / Honest / Smallbusiness</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>Teach one thing about numbers and honest that most people get wrong.</t>
         </is>
       </c>
-      <c r="G10" s="19" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>My honest numbers after 7 weeks</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H10" s="18" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="I10" s="24" t="inlineStr">
+      <c r="I10" s="26" t="inlineStr">
         <is>
           <t>not enough data yet</t>
         </is>
       </c>
-      <c r="J10" s="15" t="inlineStr"/>
-      <c r="K10" s="16" t="inlineStr"/>
-      <c r="L10" s="16" t="inlineStr"/>
-      <c r="M10" s="15" t="inlineStr"/>
+      <c r="J10" s="16" t="inlineStr"/>
+      <c r="K10" s="17" t="inlineStr"/>
+      <c r="L10" s="17" t="inlineStr"/>
+      <c r="M10" s="16" t="inlineStr"/>
     </row>
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="11" t="n">
@@ -1279,15 +1289,15 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>PROOF</t>
         </is>
@@ -1302,7 +1312,7 @@
           <t>Show a real result from understood and properly — where it started, what you changed, where it ended.</t>
         </is>
       </c>
-      <c r="G11" s="13" t="inlineStr">
+      <c r="G11" s="14" t="inlineStr">
         <is>
           <t>How I finally understood setup</t>
         </is>
@@ -1312,64 +1322,64 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="I11" s="14" t="inlineStr">
+      <c r="I11" s="15" t="inlineStr">
         <is>
           <t>solid evidence</t>
         </is>
       </c>
-      <c r="J11" s="15" t="inlineStr"/>
-      <c r="K11" s="16" t="inlineStr"/>
-      <c r="L11" s="16" t="inlineStr"/>
-      <c r="M11" s="15" t="inlineStr"/>
+      <c r="J11" s="16" t="inlineStr"/>
+      <c r="K11" s="17" t="inlineStr"/>
+      <c r="L11" s="17" t="inlineStr"/>
+      <c r="M11" s="16" t="inlineStr"/>
     </row>
     <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="17" t="n">
+      <c r="A12" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>ENGAGE</t>
         </is>
       </c>
-      <c r="E12" s="19" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>Public / Building / Smallbusiness</t>
         </is>
       </c>
-      <c r="F12" s="19" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>Ask your audience the one thing you most want to know about how they approach public and building.</t>
         </is>
       </c>
-      <c r="G12" s="19" t="inlineStr">
+      <c r="G12" s="21" t="inlineStr">
         <is>
           <t>Before and after 90 days</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H12" s="18" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="I12" s="20" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t>early signal</t>
         </is>
       </c>
-      <c r="J12" s="15" t="inlineStr"/>
-      <c r="K12" s="16" t="inlineStr"/>
-      <c r="L12" s="16" t="inlineStr"/>
-      <c r="M12" s="15" t="inlineStr"/>
+      <c r="J12" s="16" t="inlineStr"/>
+      <c r="K12" s="17" t="inlineStr"/>
+      <c r="L12" s="17" t="inlineStr"/>
+      <c r="M12" s="16" t="inlineStr"/>
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" s="11" t="n">
@@ -1377,15 +1387,15 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="D13" s="23" t="inlineStr">
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D13" s="25" t="inlineStr">
         <is>
           <t>OFFER</t>
         </is>
@@ -1400,7 +1410,7 @@
           <t>Make one specific, time-bound offer connected to asked and gear. Say exactly what they get and exactly what to do.</t>
         </is>
       </c>
-      <c r="G13" s="13" t="inlineStr">
+      <c r="G13" s="14" t="inlineStr">
         <is>
           <t>Last chance on this one</t>
         </is>
@@ -1410,64 +1420,64 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="I13" s="22" t="inlineStr">
+      <c r="I13" s="24" t="inlineStr">
         <is>
           <t>not enough data yet</t>
         </is>
       </c>
-      <c r="J13" s="15" t="inlineStr"/>
-      <c r="K13" s="16" t="inlineStr"/>
-      <c r="L13" s="16" t="inlineStr"/>
-      <c r="M13" s="15" t="inlineStr"/>
+      <c r="J13" s="16" t="inlineStr"/>
+      <c r="K13" s="17" t="inlineStr"/>
+      <c r="L13" s="17" t="inlineStr"/>
+      <c r="M13" s="16" t="inlineStr"/>
     </row>
     <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="17" t="n">
+      <c r="A14" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="D14" s="25" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="D14" s="27" t="inlineStr">
         <is>
           <t>MIRROR</t>
         </is>
       </c>
-      <c r="E14" s="19" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>Looked / Howto</t>
         </is>
       </c>
-      <c r="F14" s="19" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>Describe the frustration someone hits with looked and howto, in their words, and sell nothing.</t>
         </is>
       </c>
-      <c r="G14" s="19" t="inlineStr">
+      <c r="G14" s="21" t="inlineStr">
         <is>
           <t>framing explained properly, no jargon</t>
         </is>
       </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="H14" s="18" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="I14" s="24" t="inlineStr">
+      <c r="I14" s="26" t="inlineStr">
         <is>
           <t>not enough data yet</t>
         </is>
       </c>
-      <c r="J14" s="15" t="inlineStr"/>
-      <c r="K14" s="16" t="inlineStr"/>
-      <c r="L14" s="16" t="inlineStr"/>
-      <c r="M14" s="15" t="inlineStr"/>
+      <c r="J14" s="16" t="inlineStr"/>
+      <c r="K14" s="17" t="inlineStr"/>
+      <c r="L14" s="17" t="inlineStr"/>
+      <c r="M14" s="16" t="inlineStr"/>
     </row>
     <row r="15" ht="40" customHeight="1">
       <c r="A15" s="11" t="n">
@@ -1475,12 +1485,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -1498,7 +1508,7 @@
           <t>Teach one thing about replying and pricing that most people get wrong.</t>
         </is>
       </c>
-      <c r="G15" s="13" t="inlineStr">
+      <c r="G15" s="14" t="inlineStr">
         <is>
           <t>Grab this before it goes</t>
         </is>
@@ -1508,64 +1518,64 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="I15" s="22" t="inlineStr">
+      <c r="I15" s="24" t="inlineStr">
         <is>
           <t>not enough data yet</t>
         </is>
       </c>
-      <c r="J15" s="15" t="inlineStr"/>
-      <c r="K15" s="16" t="inlineStr"/>
-      <c r="L15" s="16" t="inlineStr"/>
-      <c r="M15" s="15" t="inlineStr"/>
+      <c r="J15" s="16" t="inlineStr"/>
+      <c r="K15" s="17" t="inlineStr"/>
+      <c r="L15" s="17" t="inlineStr"/>
+      <c r="M15" s="16" t="inlineStr"/>
     </row>
     <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="17" t="n">
+      <c r="A16" s="18" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
         <is>
           <t>PROOF</t>
         </is>
       </c>
-      <c r="E16" s="19" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>Numbers / Honest / Smallbusiness</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>Show a real result from numbers and honest — where it started, what you changed, where it ended.</t>
         </is>
       </c>
-      <c r="G16" s="19" t="inlineStr">
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>New drop out now, link in bio</t>
         </is>
       </c>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="H16" s="18" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="I16" s="24" t="inlineStr">
+      <c r="I16" s="26" t="inlineStr">
         <is>
           <t>not enough data yet</t>
         </is>
       </c>
-      <c r="J16" s="15" t="inlineStr"/>
-      <c r="K16" s="16" t="inlineStr"/>
-      <c r="L16" s="16" t="inlineStr"/>
-      <c r="M16" s="15" t="inlineStr"/>
+      <c r="J16" s="16" t="inlineStr"/>
+      <c r="K16" s="17" t="inlineStr"/>
+      <c r="L16" s="17" t="inlineStr"/>
+      <c r="M16" s="16" t="inlineStr"/>
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" s="11" t="n">
@@ -1573,15 +1583,15 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Sun</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="inlineStr">
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>ENGAGE</t>
         </is>
@@ -1602,60 +1612,60 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="I17" s="14" t="inlineStr">
+      <c r="I17" s="15" t="inlineStr">
         <is>
           <t>solid evidence</t>
         </is>
       </c>
-      <c r="J17" s="15" t="inlineStr"/>
-      <c r="K17" s="16" t="inlineStr"/>
-      <c r="L17" s="16" t="inlineStr"/>
-      <c r="M17" s="15" t="inlineStr"/>
+      <c r="J17" s="16" t="inlineStr"/>
+      <c r="K17" s="17" t="inlineStr"/>
+      <c r="L17" s="17" t="inlineStr"/>
+      <c r="M17" s="16" t="inlineStr"/>
     </row>
     <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="17" t="n">
+      <c r="A18" s="18" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="D18" s="25" t="inlineStr">
         <is>
           <t>OFFER</t>
         </is>
       </c>
-      <c r="E18" s="19" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>Public / Building / Smallbusiness</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>Make one specific, time-bound offer connected to public and building. Say exactly what they get and exactly what to do.</t>
         </is>
       </c>
-      <c r="G18" s="19" t="inlineStr"/>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr"/>
+      <c r="H18" s="18" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="I18" s="20" t="inlineStr">
+      <c r="I18" s="22" t="inlineStr">
         <is>
           <t>early signal</t>
         </is>
       </c>
-      <c r="J18" s="15" t="inlineStr"/>
-      <c r="K18" s="16" t="inlineStr"/>
-      <c r="L18" s="16" t="inlineStr"/>
-      <c r="M18" s="15" t="inlineStr"/>
+      <c r="J18" s="16" t="inlineStr"/>
+      <c r="K18" s="17" t="inlineStr"/>
+      <c r="L18" s="17" t="inlineStr"/>
+      <c r="M18" s="16" t="inlineStr"/>
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" s="11" t="n">
@@ -1663,15 +1673,15 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D19" s="25" t="inlineStr">
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="inlineStr">
         <is>
           <t>MIRROR</t>
         </is>
@@ -1692,28 +1702,28 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="I19" s="22" t="inlineStr">
+      <c r="I19" s="24" t="inlineStr">
         <is>
           <t>not enough data yet</t>
         </is>
       </c>
-      <c r="J19" s="15" t="inlineStr"/>
-      <c r="K19" s="16" t="inlineStr"/>
-      <c r="L19" s="16" t="inlineStr"/>
-      <c r="M19" s="15" t="inlineStr"/>
+      <c r="J19" s="16" t="inlineStr"/>
+      <c r="K19" s="17" t="inlineStr"/>
+      <c r="L19" s="17" t="inlineStr"/>
+      <c r="M19" s="16" t="inlineStr"/>
     </row>
     <row r="20" ht="40" customHeight="1">
-      <c r="A20" s="17" t="n">
+      <c r="A20" s="18" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
@@ -1721,31 +1731,31 @@
           <t>EDUCATE</t>
         </is>
       </c>
-      <c r="E20" s="19" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>Looked / Howto</t>
         </is>
       </c>
-      <c r="F20" s="19" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>Teach one thing about looked and howto that most people get wrong.</t>
         </is>
       </c>
-      <c r="G20" s="19" t="inlineStr"/>
-      <c r="H20" s="17" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr"/>
+      <c r="H20" s="18" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="I20" s="24" t="inlineStr">
+      <c r="I20" s="26" t="inlineStr">
         <is>
           <t>not enough data yet</t>
         </is>
       </c>
-      <c r="J20" s="15" t="inlineStr"/>
-      <c r="K20" s="16" t="inlineStr"/>
-      <c r="L20" s="16" t="inlineStr"/>
-      <c r="M20" s="15" t="inlineStr"/>
+      <c r="J20" s="16" t="inlineStr"/>
+      <c r="K20" s="17" t="inlineStr"/>
+      <c r="L20" s="17" t="inlineStr"/>
+      <c r="M20" s="16" t="inlineStr"/>
     </row>
     <row r="21" ht="40" customHeight="1">
       <c r="A21" s="11" t="n">
@@ -1753,15 +1763,15 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="D21" s="19" t="inlineStr">
         <is>
           <t>PROOF</t>
         </is>
@@ -1782,60 +1792,60 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="I21" s="22" t="inlineStr">
+      <c r="I21" s="24" t="inlineStr">
         <is>
           <t>not enough data yet</t>
         </is>
       </c>
-      <c r="J21" s="15" t="inlineStr"/>
-      <c r="K21" s="16" t="inlineStr"/>
-      <c r="L21" s="16" t="inlineStr"/>
-      <c r="M21" s="15" t="inlineStr"/>
+      <c r="J21" s="16" t="inlineStr"/>
+      <c r="K21" s="17" t="inlineStr"/>
+      <c r="L21" s="17" t="inlineStr"/>
+      <c r="M21" s="16" t="inlineStr"/>
     </row>
     <row r="22" ht="40" customHeight="1">
-      <c r="A22" s="17" t="n">
+      <c r="A22" s="18" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="D22" s="21" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>ENGAGE</t>
         </is>
       </c>
-      <c r="E22" s="19" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>Numbers / Honest / Smallbusiness</t>
         </is>
       </c>
-      <c r="F22" s="19" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>Ask your audience the one thing you most want to know about how they approach numbers and honest.</t>
         </is>
       </c>
-      <c r="G22" s="19" t="inlineStr"/>
-      <c r="H22" s="17" t="inlineStr">
+      <c r="G22" s="20" t="inlineStr"/>
+      <c r="H22" s="18" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="I22" s="24" t="inlineStr">
+      <c r="I22" s="26" t="inlineStr">
         <is>
           <t>not enough data yet</t>
         </is>
       </c>
-      <c r="J22" s="15" t="inlineStr"/>
-      <c r="K22" s="16" t="inlineStr"/>
-      <c r="L22" s="16" t="inlineStr"/>
-      <c r="M22" s="15" t="inlineStr"/>
+      <c r="J22" s="16" t="inlineStr"/>
+      <c r="K22" s="17" t="inlineStr"/>
+      <c r="L22" s="17" t="inlineStr"/>
+      <c r="M22" s="16" t="inlineStr"/>
     </row>
     <row r="23" ht="40" customHeight="1">
       <c r="A23" s="11" t="n">
@@ -1843,15 +1853,15 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="D23" s="23" t="inlineStr">
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="D23" s="25" t="inlineStr">
         <is>
           <t>OFFER</t>
         </is>
@@ -1872,60 +1882,60 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="I23" s="14" t="inlineStr">
+      <c r="I23" s="15" t="inlineStr">
         <is>
           <t>solid evidence</t>
         </is>
       </c>
-      <c r="J23" s="15" t="inlineStr"/>
-      <c r="K23" s="16" t="inlineStr"/>
-      <c r="L23" s="16" t="inlineStr"/>
-      <c r="M23" s="15" t="inlineStr"/>
+      <c r="J23" s="16" t="inlineStr"/>
+      <c r="K23" s="17" t="inlineStr"/>
+      <c r="L23" s="17" t="inlineStr"/>
+      <c r="M23" s="16" t="inlineStr"/>
     </row>
     <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="17" t="n">
+      <c r="A24" s="18" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>Sun</t>
-        </is>
-      </c>
-      <c r="D24" s="25" t="inlineStr">
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D24" s="27" t="inlineStr">
         <is>
           <t>MIRROR</t>
         </is>
       </c>
-      <c r="E24" s="19" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>Public / Building / Smallbusiness</t>
         </is>
       </c>
-      <c r="F24" s="19" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>Describe the frustration someone hits with public and building, in their words, and sell nothing.</t>
         </is>
       </c>
-      <c r="G24" s="19" t="inlineStr"/>
-      <c r="H24" s="17" t="inlineStr">
+      <c r="G24" s="20" t="inlineStr"/>
+      <c r="H24" s="18" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="I24" s="20" t="inlineStr">
+      <c r="I24" s="22" t="inlineStr">
         <is>
           <t>early signal</t>
         </is>
       </c>
-      <c r="J24" s="15" t="inlineStr"/>
-      <c r="K24" s="16" t="inlineStr"/>
-      <c r="L24" s="16" t="inlineStr"/>
-      <c r="M24" s="15" t="inlineStr"/>
+      <c r="J24" s="16" t="inlineStr"/>
+      <c r="K24" s="17" t="inlineStr"/>
+      <c r="L24" s="17" t="inlineStr"/>
+      <c r="M24" s="16" t="inlineStr"/>
     </row>
     <row r="25" ht="40" customHeight="1">
       <c r="A25" s="11" t="n">
@@ -1933,12 +1943,12 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -1962,60 +1972,60 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="I25" s="22" t="inlineStr">
+      <c r="I25" s="24" t="inlineStr">
         <is>
           <t>not enough data yet</t>
         </is>
       </c>
-      <c r="J25" s="15" t="inlineStr"/>
-      <c r="K25" s="16" t="inlineStr"/>
-      <c r="L25" s="16" t="inlineStr"/>
-      <c r="M25" s="15" t="inlineStr"/>
+      <c r="J25" s="16" t="inlineStr"/>
+      <c r="K25" s="17" t="inlineStr"/>
+      <c r="L25" s="17" t="inlineStr"/>
+      <c r="M25" s="16" t="inlineStr"/>
     </row>
     <row r="26" ht="40" customHeight="1">
-      <c r="A26" s="17" t="n">
+      <c r="A26" s="18" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="D26" s="19" t="inlineStr">
         <is>
           <t>PROOF</t>
         </is>
       </c>
-      <c r="E26" s="19" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>Looked / Howto</t>
         </is>
       </c>
-      <c r="F26" s="19" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>Show a real result from looked and howto — where it started, what you changed, where it ended.</t>
         </is>
       </c>
-      <c r="G26" s="19" t="inlineStr"/>
-      <c r="H26" s="17" t="inlineStr">
+      <c r="G26" s="20" t="inlineStr"/>
+      <c r="H26" s="18" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="I26" s="24" t="inlineStr">
+      <c r="I26" s="26" t="inlineStr">
         <is>
           <t>not enough data yet</t>
         </is>
       </c>
-      <c r="J26" s="15" t="inlineStr"/>
-      <c r="K26" s="16" t="inlineStr"/>
-      <c r="L26" s="16" t="inlineStr"/>
-      <c r="M26" s="15" t="inlineStr"/>
+      <c r="J26" s="16" t="inlineStr"/>
+      <c r="K26" s="17" t="inlineStr"/>
+      <c r="L26" s="17" t="inlineStr"/>
+      <c r="M26" s="16" t="inlineStr"/>
     </row>
     <row r="27" ht="40" customHeight="1">
       <c r="A27" s="11" t="n">
@@ -2023,15 +2033,15 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="D27" s="21" t="inlineStr">
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
         <is>
           <t>ENGAGE</t>
         </is>
@@ -2052,60 +2062,60 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="I27" s="22" t="inlineStr">
+      <c r="I27" s="24" t="inlineStr">
         <is>
           <t>not enough data yet</t>
         </is>
       </c>
-      <c r="J27" s="15" t="inlineStr"/>
-      <c r="K27" s="16" t="inlineStr"/>
-      <c r="L27" s="16" t="inlineStr"/>
-      <c r="M27" s="15" t="inlineStr"/>
+      <c r="J27" s="16" t="inlineStr"/>
+      <c r="K27" s="17" t="inlineStr"/>
+      <c r="L27" s="17" t="inlineStr"/>
+      <c r="M27" s="16" t="inlineStr"/>
     </row>
     <row r="28" ht="40" customHeight="1">
-      <c r="A28" s="17" t="n">
+      <c r="A28" s="18" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="D28" s="23" t="inlineStr">
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="D28" s="25" t="inlineStr">
         <is>
           <t>OFFER</t>
         </is>
       </c>
-      <c r="E28" s="19" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>Numbers / Honest / Smallbusiness</t>
         </is>
       </c>
-      <c r="F28" s="19" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>Make one specific, time-bound offer connected to numbers and honest. Say exactly what they get and exactly what to do.</t>
         </is>
       </c>
-      <c r="G28" s="19" t="inlineStr"/>
-      <c r="H28" s="17" t="inlineStr">
+      <c r="G28" s="20" t="inlineStr"/>
+      <c r="H28" s="18" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="I28" s="24" t="inlineStr">
+      <c r="I28" s="26" t="inlineStr">
         <is>
           <t>not enough data yet</t>
         </is>
       </c>
-      <c r="J28" s="15" t="inlineStr"/>
-      <c r="K28" s="16" t="inlineStr"/>
-      <c r="L28" s="16" t="inlineStr"/>
-      <c r="M28" s="15" t="inlineStr"/>
+      <c r="J28" s="16" t="inlineStr"/>
+      <c r="K28" s="17" t="inlineStr"/>
+      <c r="L28" s="17" t="inlineStr"/>
+      <c r="M28" s="16" t="inlineStr"/>
     </row>
     <row r="29" ht="40" customHeight="1">
       <c r="A29" s="11" t="n">
@@ -2113,15 +2123,15 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="D29" s="25" t="inlineStr">
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="D29" s="27" t="inlineStr">
         <is>
           <t>MIRROR</t>
         </is>
@@ -2142,28 +2152,28 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="I29" s="14" t="inlineStr">
+      <c r="I29" s="15" t="inlineStr">
         <is>
           <t>solid evidence</t>
         </is>
       </c>
-      <c r="J29" s="15" t="inlineStr"/>
-      <c r="K29" s="16" t="inlineStr"/>
-      <c r="L29" s="16" t="inlineStr"/>
-      <c r="M29" s="15" t="inlineStr"/>
+      <c r="J29" s="16" t="inlineStr"/>
+      <c r="K29" s="17" t="inlineStr"/>
+      <c r="L29" s="17" t="inlineStr"/>
+      <c r="M29" s="16" t="inlineStr"/>
     </row>
     <row r="30" ht="40" customHeight="1">
-      <c r="A30" s="17" t="n">
+      <c r="A30" s="18" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="inlineStr">
-        <is>
-          <t>Sat</t>
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
@@ -2171,31 +2181,31 @@
           <t>EDUCATE</t>
         </is>
       </c>
-      <c r="E30" s="19" t="inlineStr">
+      <c r="E30" s="20" t="inlineStr">
         <is>
           <t>Public / Building / Smallbusiness</t>
         </is>
       </c>
-      <c r="F30" s="19" t="inlineStr">
+      <c r="F30" s="20" t="inlineStr">
         <is>
           <t>Teach one thing about public and building that most people get wrong.</t>
         </is>
       </c>
-      <c r="G30" s="19" t="inlineStr"/>
-      <c r="H30" s="17" t="inlineStr">
+      <c r="G30" s="20" t="inlineStr"/>
+      <c r="H30" s="18" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="I30" s="20" t="inlineStr">
+      <c r="I30" s="22" t="inlineStr">
         <is>
           <t>early signal</t>
         </is>
       </c>
-      <c r="J30" s="15" t="inlineStr"/>
-      <c r="K30" s="16" t="inlineStr"/>
-      <c r="L30" s="16" t="inlineStr"/>
-      <c r="M30" s="15" t="inlineStr"/>
+      <c r="J30" s="16" t="inlineStr"/>
+      <c r="K30" s="17" t="inlineStr"/>
+      <c r="L30" s="17" t="inlineStr"/>
+      <c r="M30" s="16" t="inlineStr"/>
     </row>
     <row r="31" ht="40" customHeight="1">
       <c r="A31" s="11" t="n">
@@ -2203,15 +2213,15 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Sun</t>
-        </is>
-      </c>
-      <c r="D31" s="18" t="inlineStr">
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D31" s="19" t="inlineStr">
         <is>
           <t>PROOF</t>
         </is>
@@ -2232,60 +2242,60 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="I31" s="22" t="inlineStr">
+      <c r="I31" s="24" t="inlineStr">
         <is>
           <t>not enough data yet</t>
         </is>
       </c>
-      <c r="J31" s="15" t="inlineStr"/>
-      <c r="K31" s="16" t="inlineStr"/>
-      <c r="L31" s="16" t="inlineStr"/>
-      <c r="M31" s="15" t="inlineStr"/>
+      <c r="J31" s="16" t="inlineStr"/>
+      <c r="K31" s="17" t="inlineStr"/>
+      <c r="L31" s="17" t="inlineStr"/>
+      <c r="M31" s="16" t="inlineStr"/>
     </row>
     <row r="32" ht="40" customHeight="1">
-      <c r="A32" s="17" t="n">
+      <c r="A32" s="18" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C32" s="17" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="D32" s="21" t="inlineStr">
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="inlineStr">
         <is>
           <t>ENGAGE</t>
         </is>
       </c>
-      <c r="E32" s="19" t="inlineStr">
+      <c r="E32" s="20" t="inlineStr">
         <is>
           <t>Looked / Howto</t>
         </is>
       </c>
-      <c r="F32" s="19" t="inlineStr">
+      <c r="F32" s="20" t="inlineStr">
         <is>
           <t>Ask your audience the one thing you most want to know about how they approach looked and howto.</t>
         </is>
       </c>
-      <c r="G32" s="19" t="inlineStr"/>
-      <c r="H32" s="17" t="inlineStr">
+      <c r="G32" s="20" t="inlineStr"/>
+      <c r="H32" s="18" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="I32" s="24" t="inlineStr">
+      <c r="I32" s="26" t="inlineStr">
         <is>
           <t>not enough data yet</t>
         </is>
       </c>
-      <c r="J32" s="15" t="inlineStr"/>
-      <c r="K32" s="16" t="inlineStr"/>
-      <c r="L32" s="16" t="inlineStr"/>
-      <c r="M32" s="15" t="inlineStr"/>
+      <c r="J32" s="16" t="inlineStr"/>
+      <c r="K32" s="17" t="inlineStr"/>
+      <c r="L32" s="17" t="inlineStr"/>
+      <c r="M32" s="16" t="inlineStr"/>
     </row>
     <row r="33" ht="40" customHeight="1">
       <c r="A33" s="11" t="n">
@@ -2293,15 +2303,15 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D33" s="23" t="inlineStr">
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="D33" s="25" t="inlineStr">
         <is>
           <t>OFFER</t>
         </is>
@@ -2322,60 +2332,60 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="I33" s="22" t="inlineStr">
+      <c r="I33" s="24" t="inlineStr">
         <is>
           <t>not enough data yet</t>
         </is>
       </c>
-      <c r="J33" s="15" t="inlineStr"/>
-      <c r="K33" s="16" t="inlineStr"/>
-      <c r="L33" s="16" t="inlineStr"/>
-      <c r="M33" s="15" t="inlineStr"/>
+      <c r="J33" s="16" t="inlineStr"/>
+      <c r="K33" s="17" t="inlineStr"/>
+      <c r="L33" s="17" t="inlineStr"/>
+      <c r="M33" s="16" t="inlineStr"/>
     </row>
     <row r="34" ht="40" customHeight="1">
-      <c r="A34" s="17" t="n">
+      <c r="A34" s="18" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C34" s="17" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="D34" s="25" t="inlineStr">
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D34" s="27" t="inlineStr">
         <is>
           <t>MIRROR</t>
         </is>
       </c>
-      <c r="E34" s="19" t="inlineStr">
+      <c r="E34" s="20" t="inlineStr">
         <is>
           <t>Numbers / Honest / Smallbusiness</t>
         </is>
       </c>
-      <c r="F34" s="19" t="inlineStr">
+      <c r="F34" s="20" t="inlineStr">
         <is>
           <t>Describe the frustration someone hits with numbers and honest, in their words, and sell nothing.</t>
         </is>
       </c>
-      <c r="G34" s="19" t="inlineStr"/>
-      <c r="H34" s="17" t="inlineStr">
+      <c r="G34" s="20" t="inlineStr"/>
+      <c r="H34" s="18" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="I34" s="24" t="inlineStr">
+      <c r="I34" s="26" t="inlineStr">
         <is>
           <t>not enough data yet</t>
         </is>
       </c>
-      <c r="J34" s="15" t="inlineStr"/>
-      <c r="K34" s="16" t="inlineStr"/>
-      <c r="L34" s="16" t="inlineStr"/>
-      <c r="M34" s="15" t="inlineStr"/>
+      <c r="J34" s="16" t="inlineStr"/>
+      <c r="K34" s="17" t="inlineStr"/>
+      <c r="L34" s="17" t="inlineStr"/>
+      <c r="M34" s="16" t="inlineStr"/>
     </row>
     <row r="35"/>
     <row r="36">
@@ -2391,6 +2401,20 @@
       <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2453,10 +2477,10 @@
           <t>Before and after 90 days</t>
         </is>
       </c>
-      <c r="B5" s="26" t="n">
+      <c r="B5" s="28" t="n">
         <v>20756</v>
       </c>
-      <c r="C5" s="27" t="n">
+      <c r="C5" s="29" t="n">
         <v>6.55</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -2471,10 +2495,10 @@
           <t>3 ways to fix your framing in under a minute</t>
         </is>
       </c>
-      <c r="B6" s="26" t="n">
+      <c r="B6" s="28" t="n">
         <v>17201</v>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="29" t="n">
         <v>5.43</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -2489,10 +2513,10 @@
           <t>How I finally understood setup</t>
         </is>
       </c>
-      <c r="B7" s="26" t="n">
+      <c r="B7" s="28" t="n">
         <v>16629</v>
       </c>
-      <c r="C7" s="27" t="n">
+      <c r="C7" s="29" t="n">
         <v>5.25</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -2507,10 +2531,10 @@
           <t>Replying to a comment about software</t>
         </is>
       </c>
-      <c r="B8" s="26" t="n">
+      <c r="B8" s="28" t="n">
         <v>15181</v>
       </c>
-      <c r="C8" s="27" t="n">
+      <c r="C8" s="29" t="n">
         <v>4.79</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -2525,10 +2549,10 @@
           <t>Day 30 of building this in public</t>
         </is>
       </c>
-      <c r="B9" s="26" t="n">
+      <c r="B9" s="28" t="n">
         <v>12637</v>
       </c>
-      <c r="C9" s="27" t="n">
+      <c r="C9" s="29" t="n">
         <v>3.99</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -2543,10 +2567,10 @@
           <t>Last chance on this one</t>
         </is>
       </c>
-      <c r="B10" s="26" t="n">
+      <c r="B10" s="28" t="n">
         <v>8382</v>
       </c>
-      <c r="C10" s="27" t="n">
+      <c r="C10" s="29" t="n">
         <v>2.65</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -2561,10 +2585,10 @@
           <t>framing explained properly, no jargon</t>
         </is>
       </c>
-      <c r="B11" s="26" t="n">
+      <c r="B11" s="28" t="n">
         <v>8183</v>
       </c>
-      <c r="C11" s="27" t="n">
+      <c r="C11" s="29" t="n">
         <v>2.58</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -2579,10 +2603,10 @@
           <t>What 30 months of this actually looked like</t>
         </is>
       </c>
-      <c r="B12" s="26" t="n">
+      <c r="B12" s="28" t="n">
         <v>7736</v>
       </c>
-      <c r="C12" s="27" t="n">
+      <c r="C12" s="29" t="n">
         <v>2.44</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -2597,10 +2621,10 @@
           <t>Grab this before it goes</t>
         </is>
       </c>
-      <c r="B13" s="26" t="n">
+      <c r="B13" s="28" t="n">
         <v>6517</v>
       </c>
-      <c r="C13" s="27" t="n">
+      <c r="C13" s="29" t="n">
         <v>2.06</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -2615,10 +2639,10 @@
           <t>You asked, so here it is: gear</t>
         </is>
       </c>
-      <c r="B14" s="26" t="n">
+      <c r="B14" s="28" t="n">
         <v>6260</v>
       </c>
-      <c r="C14" s="27" t="n">
+      <c r="C14" s="29" t="n">
         <v>1.98</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -2633,10 +2657,10 @@
           <t>New drop out now, link in bio</t>
         </is>
       </c>
-      <c r="B15" s="26" t="n">
+      <c r="B15" s="28" t="n">
         <v>6258</v>
       </c>
-      <c r="C15" s="27" t="n">
+      <c r="C15" s="29" t="n">
         <v>1.98</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -2651,10 +2675,10 @@
           <t>My honest numbers after 7 weeks</t>
         </is>
       </c>
-      <c r="B16" s="26" t="n">
+      <c r="B16" s="28" t="n">
         <v>5770</v>
       </c>
-      <c r="C16" s="27" t="n">
+      <c r="C16" s="29" t="n">
         <v>1.82</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -2747,7 +2771,7 @@
       </c>
     </row>
     <row r="5" ht="38" customHeight="1">
-      <c r="A5" s="28" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>EDUCATE</t>
         </is>
@@ -2755,7 +2779,7 @@
       <c r="B5" t="n">
         <v>6</v>
       </c>
-      <c r="C5" s="27" t="n">
+      <c r="C5" s="29" t="n">
         <v>0.2</v>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -2765,7 +2789,7 @@
       </c>
     </row>
     <row r="6" ht="38" customHeight="1">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>PROOF</t>
         </is>
@@ -2773,7 +2797,7 @@
       <c r="B6" t="n">
         <v>6</v>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="29" t="n">
         <v>0.2</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -2783,7 +2807,7 @@
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
-      <c r="A7" s="30" t="inlineStr">
+      <c r="A7" s="32" t="inlineStr">
         <is>
           <t>ENGAGE</t>
         </is>
@@ -2791,7 +2815,7 @@
       <c r="B7" t="n">
         <v>6</v>
       </c>
-      <c r="C7" s="27" t="n">
+      <c r="C7" s="29" t="n">
         <v>0.2</v>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -2801,7 +2825,7 @@
       </c>
     </row>
     <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="31" t="inlineStr">
+      <c r="A8" s="33" t="inlineStr">
         <is>
           <t>OFFER</t>
         </is>
@@ -2809,17 +2833,17 @@
       <c r="B8" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="27" t="n">
+      <c r="C8" s="29" t="n">
         <v>0.2</v>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>The direct revenue driver. One per five days is the right frequency — more than that and it reads as desperate.</t>
+          <t>The direct sales post. One every five days is right — more, and it reads as desperate.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1">
-      <c r="A9" s="32" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>MIRROR</t>
         </is>
@@ -2827,7 +2851,7 @@
       <c r="B9" t="n">
         <v>6</v>
       </c>
-      <c r="C9" s="27" t="n">
+      <c r="C9" s="29" t="n">
         <v>0.2</v>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -2977,7 +3001,7 @@
           <t>Consistency</t>
         </is>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="29">
         <f>IF(B5=0,0,B6/B5)</f>
         <v/>
       </c>
